--- a/themes/mobileAppProblems.xlsx
+++ b/themes/mobileAppProblems.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -530,99 +530,79 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Номер карты Уралсиб указан на лицевой стороне карты и состоит из 16-ти цифр. Также при регистрации можно использовать 20-значный номер счета, указанный в документах при оформлении договора</t>
+          <t xml:space="preserve">  Пароль был выслан вам в СМС сообщении от банка. Если вы уже заходили с ним и изменили пароль, то воспользуйтесь собственным паролем. Если забыли текущий пароль:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Номер карты Уралсиб указан на лицевой стороне карты и состоит из 16-ти цифр. Также при регистрации можно использовать 20-значный номер счета, указанный в документах при оформлении договора.</t>
+          <t xml:space="preserve">  Пароль был выслан вам в SMS-сообщении от банка. Если вы уже заходили с ним и изменили пароль, то воспользуйтесь собственным паролем. Если забыли текущий пароль:</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>«СМС сообщении» приведено к «SMS-сообщении» — для единообразия с остальными случаями в базе</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Пароль был выслан вам в СМС сообщении от банка. Если вы уже заходили с ним и изменили пароль, то воспользуйтесь собственным паролем. Если забыли текущий пароль:</t>
+          <t xml:space="preserve">  Ошибка авторизации по биометрии может возникать по причине смены или сбое настроек телефона. </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Пароль был выслан вам в SMS-сообщении от банка. Если вы уже заходили с ним и изменили пароль, то воспользуйтесь собственным паролем. Если забыли текущий пароль:</t>
+          <t xml:space="preserve">  Ошибка авторизации по биометрии может возникать по причине смены или сбоя настроек телефона. </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>«СМС сообщении» приведено к «SMS-сообщении» — для единообразия с остальными случаями в базе</t>
+          <t>«сбое» исправлено на «сбоя» — согласование падежа с «смены» (родительный падеж после «причине»)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ошибка авторизации по биометрии может возникать по причине смены или сбое настроек телефона. </t>
+          <t xml:space="preserve">  Обновление происходит автоматически при входе в систему. Иногда, при нестабильном интернет соединении, этого не происходит. Попробуйте обновить экран вручную свайпом, протянув пальцем в приложении сверху вниз.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ошибка авторизации по биометрии может возникать по причине смены или сбоя настроек телефона. </t>
+          <t xml:space="preserve">  Обновление происходит автоматически при входе в систему. Иногда, при нестабильном интернет-соединении, этого не происходит. Попробуйте обновить экран вручную свайпом, протянув пальцем в приложении сверху вниз.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>«сбое» исправлено на «сбоя» — согласование падежа с «смены» (родительный падеж после «причине»)</t>
+          <t>составное слово «интернет-соединении» пишется через дефис</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Обновление происходит автоматически при входе в систему. Иногда, при нестабильном интернет соединении, этого не происходит. Попробуйте обновить экран вручную свайпом, протянув пальцем в приложении сверху вниз.</t>
+          <t xml:space="preserve">   • Продукт в процессе открытия – данная ситуация длится не более суток. Пожалуйста, проверьте информацию позднее.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Обновление происходит автоматически при входе в систему. Иногда, при нестабильном интернет-соединении, этого не происходит. Попробуйте обновить экран вручную свайпом, протянув пальцем в приложении сверху вниз.</t>
+          <t xml:space="preserve">   • Продукт в процессе открытия — данная ситуация длится не более суток. Пожалуйста, проверьте информацию позднее.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>составное слово «интернет-соединении» пишется через дефис</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>144</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Продукт в процессе открытия – данная ситуация длится не более суток. Пожалуйста, проверьте информацию позднее.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Продукт в процессе открытия — данная ситуация длится не более суток. Пожалуйста, проверьте информацию позднее.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
         <is>
           <t>эн-дефис (–) заменён на тире (—)</t>
         </is>
